--- a/content/production-closure/live-customer-commercial-convergence/financial-document-intelligence-staging-s1/documents/synthetic-statements.xlsx
+++ b/content/production-closure/live-customer-commercial-convergence/financial-document-intelligence-staging-s1/documents/synthetic-statements.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="1" r:id="Rca39e3ff74294be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="1" r:id="Rc39f4cb3f2e44d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviewed" sheetId="2" r:id="R165e563f91ef4ce5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,8 +14,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0.00;(#,##0.00)"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -52,11 +54,21 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -299,7 +311,7 @@
         <x:v>186000</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>2025-Q1</x:v>
@@ -322,7 +334,7 @@
         <x:v>102000</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>2025-Q1</x:v>
@@ -345,7 +357,7 @@
         <x:v>51000</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>2025-Q1</x:v>
@@ -368,7 +380,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>2025-Q1</x:v>
@@ -391,7 +403,7 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>2025-Q1</x:v>
@@ -414,7 +426,7 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>2025-Q1</x:v>
@@ -437,7 +449,7 @@
         <x:v>224000</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>2025-Q2</x:v>
@@ -460,7 +472,7 @@
         <x:v>128000</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D9" t="str">
         <x:v>2025-Q2</x:v>
@@ -483,7 +495,7 @@
         <x:v>58000</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D10" t="str">
         <x:v>2025-Q2</x:v>
@@ -506,7 +518,7 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D11" t="str">
         <x:v>2025-Q2</x:v>
@@ -529,7 +541,7 @@
         <x:v>8000</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>2025-Q2</x:v>
@@ -552,7 +564,7 @@
         <x:v>27000</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>2025-Q2</x:v>
@@ -575,7 +587,7 @@
         <x:v>84000</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>2025-Q1</x:v>
@@ -598,7 +610,7 @@
         <x:v>32000</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D15" t="str">
         <x:v>2025-Q1</x:v>
@@ -621,7 +633,7 @@
         <x:v>16000</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D16" t="str">
         <x:v>2025-Q1</x:v>
@@ -644,7 +656,7 @@
         <x:v>42000</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D17" t="str">
         <x:v>2025-Q1</x:v>
@@ -667,7 +679,7 @@
         <x:v>22000</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D18" t="str">
         <x:v>2025-Q1</x:v>
@@ -690,7 +702,7 @@
         <x:v>26000</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D19" t="str">
         <x:v>2025-Q1</x:v>
@@ -713,7 +725,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>2025-Q1</x:v>
@@ -736,7 +748,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>2025-Q1</x:v>
@@ -759,7 +771,7 @@
         <x:v>134000</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>2025-Q1</x:v>
@@ -782,7 +794,7 @@
         <x:v>72000</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>2025-Q1</x:v>
@@ -805,7 +817,7 @@
         <x:v>62000</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D24" t="str">
         <x:v>2025-Q1</x:v>
@@ -828,7 +840,7 @@
         <x:v>100000</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D25" t="str">
         <x:v>2025-Q2</x:v>
@@ -851,7 +863,7 @@
         <x:v>43000</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D26" t="str">
         <x:v>2025-Q2</x:v>
@@ -874,7 +886,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D27" t="str">
         <x:v>2025-Q2</x:v>
@@ -897,7 +909,7 @@
         <x:v>61000</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>2025-Q2</x:v>
@@ -920,7 +932,7 @@
         <x:v>31000</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>2025-Q2</x:v>
@@ -943,7 +955,7 @@
         <x:v>34000</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>2025-Q2</x:v>
@@ -966,7 +978,7 @@
         <x:v>56000</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>2025-Q2</x:v>
@@ -989,7 +1001,7 @@
         <x:v>62000</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>2025-Q2</x:v>
@@ -1012,7 +1024,7 @@
         <x:v>162000</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>2025-Q2</x:v>
@@ -1035,7 +1047,7 @@
         <x:v>87000</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>2025-Q2</x:v>
@@ -1058,7 +1070,7 @@
         <x:v>75000</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>2025-Q2</x:v>
@@ -1081,7 +1093,7 @@
         <x:v>14000</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D36" t="str">
         <x:v>2025-Q1</x:v>
@@ -1104,7 +1116,7 @@
         <x:v>18000</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D37" t="str">
         <x:v>2025-Q1</x:v>
@@ -1127,7 +1139,7 @@
         <x:v>-7000</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D38" t="str">
         <x:v>2025-Q1</x:v>
@@ -1150,7 +1162,7 @@
         <x:v>-9000</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D39" t="str">
         <x:v>2025-Q1</x:v>
@@ -1173,7 +1185,7 @@
         <x:v>16000</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D40" t="str">
         <x:v>2025-Q1</x:v>
@@ -1196,7 +1208,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D41" t="str">
         <x:v>2025-Q1</x:v>
@@ -1219,7 +1231,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D42" t="str">
         <x:v>2025-Q1</x:v>
@@ -1242,7 +1254,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D43" t="str">
         <x:v>2025-Q1</x:v>
@@ -1265,7 +1277,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D44" t="str">
         <x:v>2025-Q1</x:v>
@@ -1288,7 +1300,7 @@
         <x:v>16000</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D45" t="str">
         <x:v>2025-Q2</x:v>
@@ -1311,7 +1323,7 @@
         <x:v>9000</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D46" t="str">
         <x:v>2025-Q2</x:v>
@@ -1334,7 +1346,7 @@
         <x:v>-12000</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D47" t="str">
         <x:v>2025-Q2</x:v>
@@ -1357,7 +1369,7 @@
         <x:v>-8000</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D48" t="str">
         <x:v>2025-Q2</x:v>
@@ -1380,7 +1392,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D49" t="str">
         <x:v>2025-Q2</x:v>
@@ -1403,7 +1415,7 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D50" t="str">
         <x:v>2025-Q2</x:v>
@@ -1426,7 +1438,7 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D51" t="str">
         <x:v>2025-Q2</x:v>
@@ -1449,7 +1461,7 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D52" t="str">
         <x:v>2025-Q2</x:v>
@@ -1472,7 +1484,7 @@
         <x:v>9000</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D53" t="str">
         <x:v>2025-Q2</x:v>
@@ -1495,7 +1507,7 @@
         <x:v>42000</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D54" t="str">
         <x:v>2025-Q1</x:v>
@@ -1518,7 +1530,7 @@
         <x:v>61000</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D55" t="str">
         <x:v>2025-Q2</x:v>
@@ -1541,7 +1553,7 @@
         <x:v>22000</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D56" t="str">
         <x:v>2025-Q1</x:v>
@@ -1564,7 +1576,7 @@
         <x:v>31000</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D57" t="str">
         <x:v>2025-Q2</x:v>
@@ -1587,7 +1599,7 @@
         <x:v>26000</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D58" t="str">
         <x:v>2025-Q1</x:v>
@@ -1610,7 +1622,7 @@
         <x:v>34000</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D59" t="str">
         <x:v>2025-Q2</x:v>
@@ -1633,7 +1645,7 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D60" t="str">
         <x:v>2025-Q1</x:v>
@@ -1656,7 +1668,7 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D61" t="str">
         <x:v>2025-Q1</x:v>
@@ -1679,7 +1691,7 @@
         <x:v>14000</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D62" t="str">
         <x:v>2025-Q2</x:v>
@@ -1702,7 +1714,7 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D63" t="str">
         <x:v>2025-Q2</x:v>
@@ -1725,7 +1737,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D64" t="str">
         <x:v>2025-Q1</x:v>
@@ -1748,7 +1760,7 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D65" t="str">
         <x:v>2025-Q1</x:v>
@@ -1771,7 +1783,7 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D66" t="str">
         <x:v>2025-Q1</x:v>
@@ -1794,7 +1806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D67" t="str">
         <x:v>2025-Q1</x:v>
@@ -1817,7 +1829,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D68" t="str">
         <x:v>2025-Q2</x:v>
@@ -1840,7 +1852,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D69" t="str">
         <x:v>2025-Q2</x:v>
@@ -1863,7 +1875,7 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D70" t="str">
         <x:v>2025-Q2</x:v>
@@ -1886,7 +1898,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>CURRENCY_MINOR</x:v>
+        <x:v>MYR_MAJOR</x:v>
       </x:c>
       <x:c r="D71" t="str">
         <x:v>2025-Q2</x:v>
@@ -1899,6 +1911,115 @@
       </x:c>
       <x:c r="G71" t="str">
         <x:v>2025-06-30</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="55" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Measure / 项目</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>2025-Q1 MYR</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>2025-Q2 MYR</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="str">
+        <x:v>Scope / 范围</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>毛利 / Gross profit</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="n">
+        <x:v>84000</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>96000</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>Synthetic reviewed, not audited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>净利润 / Net profit</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="n">
+        <x:v>27000</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>Synthetic reviewed, not audited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>经营现金流 / Operating cash flow</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>Synthetic reviewed, not audited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>营运资本 / Working capital</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="n">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="n">
+        <x:v>57000</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>Synthetic reviewed, not audited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>经营资金余量（非可提取资金） / Operating headroom (not withdrawable cash)</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="n">
+        <x:v>-4000</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="n">
+        <x:v>-13000</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>Synthetic reviewed, not audited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>Owner accessible cash / 可提取资金</x:v>
+      </x:c>
+      <x:c r="B7" s="7"/>
+      <x:c r="C7" s="7"/>
+      <x:c r="D7" s="6" t="str">
+        <x:v>Unknown / 未知</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
